--- a/data/trans_camb/P16A04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A04-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,03</t>
+          <t>-1,27; 1,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,62</t>
+          <t>-3,29; -0,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,91</t>
+          <t>-1,07; 2,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,42</t>
+          <t>-1,17; 1,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,02</t>
+          <t>-1,45; 1,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,14</t>
+          <t>1,05; 5,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,23</t>
+          <t>-0,99; 1,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,02</t>
+          <t>-1,91; -0,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,65</t>
+          <t>0,62; 3,7</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 83,49</t>
+          <t>-33,44; 81,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-82,24; -22,43</t>
+          <t>-80,86; -20,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 116,03</t>
+          <t>-30,91; 109,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,39; 74,14</t>
+          <t>-37,07; 69,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,1; 51,95</t>
+          <t>-49,08; 52,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,08; 234,83</t>
+          <t>31,37; 251,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 53,25</t>
+          <t>-29,32; 48,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,35; 0,18</t>
+          <t>-59,29; -1,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,74; 151,18</t>
+          <t>16,48; 148,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,48</t>
+          <t>0,5; 2,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,8</t>
+          <t>0,07; 1,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,68</t>
+          <t>-0,14; 1,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,31</t>
+          <t>-0,04; 2,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,78</t>
+          <t>-1,14; 0,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,29</t>
+          <t>-0,86; 1,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,09</t>
+          <t>0,59; 2,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,06</t>
+          <t>-0,27; 1,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,25</t>
+          <t>-0,16; 1,26</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,41; 265,1</t>
+          <t>26,43; 260,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 191,41</t>
+          <t>0,48; 190,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 170,85</t>
+          <t>-10,97; 181,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 135,35</t>
+          <t>-5,15; 126,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,89; 42,26</t>
+          <t>-41,3; 47,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 77,93</t>
+          <t>-31,09; 70,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,57; 144,33</t>
+          <t>28,87; 145,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 74,09</t>
+          <t>-13,17; 73,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 83,25</t>
+          <t>-6,86; 90,86</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,85</t>
+          <t>-0,35; 3,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,55</t>
+          <t>0,39; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,42</t>
+          <t>-0,86; 1,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,11</t>
+          <t>-1,0; 1,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,38</t>
+          <t>-0,22; 3,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,51</t>
+          <t>-0,33; 2,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,95</t>
+          <t>-0,47; 1,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,87</t>
+          <t>0,53; 2,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,61</t>
+          <t>-0,13; 1,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,67; 908,42</t>
+          <t>-52,68; 803,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1236,1</t>
+          <t>1,37; 1399,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,61; 531,77</t>
+          <t>-64,46; 458,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,79; 372,13</t>
+          <t>-71,66; 329,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,38; 511,94</t>
+          <t>-25,99; 596,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 412,73</t>
+          <t>-25,42; 499,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 312,49</t>
+          <t>-41,74; 259,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,9; 525,51</t>
+          <t>26,32; 514,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 261,04</t>
+          <t>-18,43; 284,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,86</t>
+          <t>0,24; 1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,01</t>
+          <t>-0,38; 0,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,11</t>
+          <t>-0,42; 1,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,4</t>
+          <t>-0,11; 1,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,78</t>
+          <t>-0,7; 0,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,66</t>
+          <t>0,03; 1,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,45</t>
+          <t>0,36; 1,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,63</t>
+          <t>-0,36; 0,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,18</t>
+          <t>0,01; 1,18</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,82; 124,05</t>
+          <t>10,46; 128,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 67,69</t>
+          <t>-19,65; 61,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 73,86</t>
+          <t>-20,1; 74,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 73,67</t>
+          <t>-4,18; 82,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 42,51</t>
+          <t>-27,09; 40,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 91,88</t>
+          <t>-0,02; 85,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,88; 81,48</t>
+          <t>16,28; 80,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 35,71</t>
+          <t>-16,15; 34,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 66,04</t>
+          <t>0,39; 66,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A04-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>1,59</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,98</t>
+          <t>-1,32; 2,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,6</t>
+          <t>-3,18; -0,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,83</t>
+          <t>-0,97; 2,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,34</t>
+          <t>-1,08; 1,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,06</t>
+          <t>-1,49; 1,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,19</t>
+          <t>0,75; 3,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,1</t>
+          <t>-0,85; 1,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; -0,1</t>
+          <t>-1,82; -0,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,7</t>
+          <t>0,54; 2,88</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>106,08%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>56,58%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 81,83</t>
+          <t>-35,34; 87,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,86; -20,51</t>
+          <t>-81,92; -19,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 109,2</t>
+          <t>-28,18; 114,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 69,52</t>
+          <t>-34,9; 64,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 52,51</t>
+          <t>-49,53; 58,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,37; 251,4</t>
+          <t>19,48; 190,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 48,05</t>
+          <t>-26,14; 48,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,29; -1,27</t>
+          <t>-58,93; 0,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,48; 148,79</t>
+          <t>13,14; 119,68</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,48</t>
+          <t>0,63; 2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,71</t>
+          <t>0,08; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,76</t>
+          <t>0,18; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,23</t>
+          <t>-0,01; 2,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,84</t>
+          <t>-1,17; 0,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,24</t>
+          <t>-0,36; 1,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,08</t>
+          <t>0,61; 2,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,05</t>
+          <t>-0,31; 1,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,26</t>
+          <t>0,19; 1,53</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,43; 260,8</t>
+          <t>33,54; 289,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 190,64</t>
+          <t>-0,24; 204,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 181,68</t>
+          <t>6,88; 203,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 126,52</t>
+          <t>-1,25; 148,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 47,86</t>
+          <t>-40,93; 48,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 70,37</t>
+          <t>-16,51; 97,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,87; 145,83</t>
+          <t>27,48; 151,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 73,98</t>
+          <t>-15,39; 72,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 90,86</t>
+          <t>8,14; 109,42</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,0</t>
+          <t>-0,28; 3,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,66</t>
+          <t>0,34; 3,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,39</t>
+          <t>-0,92; 1,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,87</t>
+          <t>-1,15; 1,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,25</t>
+          <t>-0,2; 3,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,41</t>
+          <t>0,11; 3,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,92</t>
+          <t>-0,43; 1,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,93</t>
+          <t>0,47; 2,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,7</t>
+          <t>-0,08; 1,83</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>125,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 803,96</t>
+          <t>-58,62; 1016,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1399,33</t>
+          <t>-9,63; 1152,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 458,15</t>
+          <t>-67,11; 411,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-71,66; 329,55</t>
+          <t>-71,01; 294,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 596,3</t>
+          <t>-27,54; 626,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 499,19</t>
+          <t>-7,5; 613,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 259,99</t>
+          <t>-43,82; 309,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,32; 514,99</t>
+          <t>13,63; 519,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 284,17</t>
+          <t>-14,39; 317,43</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,89</t>
+          <t>0,31; 1,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,93</t>
+          <t>-0,41; 0,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,12</t>
+          <t>-0,17; 1,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,5</t>
+          <t>-0,09; 1,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,72</t>
+          <t>-0,71; 0,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,62</t>
+          <t>0,33; 1,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,42</t>
+          <t>0,32; 1,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,59</t>
+          <t>-0,39; 0,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,18</t>
+          <t>0,34; 1,32</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,46; 128,18</t>
+          <t>11,9; 121,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 61,24</t>
+          <t>-19,79; 64,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 74,74</t>
+          <t>-9,67; 83,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 82,68</t>
+          <t>-4,42; 80,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 40,24</t>
+          <t>-27,28; 41,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 85,83</t>
+          <t>12,37; 95,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,28; 80,97</t>
+          <t>13,78; 81,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 34,51</t>
+          <t>-17,61; 32,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 66,55</t>
+          <t>14,27; 74,06</t>
         </is>
       </c>
     </row>
